--- a/Listing/BEV03S.xlsx
+++ b/Listing/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="401">
   <si>
     <t/>
   </si>
@@ -268,12 +268,6 @@
     <t>PDIASRE UHT VNILA100</t>
   </si>
   <si>
-    <t>20134337</t>
-  </si>
-  <si>
-    <t>PDIASRE UHT CKLAT100</t>
-  </si>
-  <si>
     <t>20046862</t>
   </si>
   <si>
@@ -304,12 +298,6 @@
     <t>F/FLAG CHOCO TPK 110</t>
   </si>
   <si>
-    <t>10034798</t>
-  </si>
-  <si>
-    <t>F/FLAG STRAW TPK 110</t>
-  </si>
-  <si>
     <t>20096322</t>
   </si>
   <si>
@@ -322,715 +310,733 @@
     <t>DANCOW FRTGO VNLA110</t>
   </si>
   <si>
+    <t>20057229</t>
+  </si>
+  <si>
+    <t>VIDORAN SUSU COK 110</t>
+  </si>
+  <si>
+    <t>20113180</t>
+  </si>
+  <si>
+    <t>MILO COKLAT 4X110ML</t>
+  </si>
+  <si>
+    <t>20083931</t>
+  </si>
+  <si>
+    <t>MILO ACT-GO 4X180ML</t>
+  </si>
+  <si>
+    <t>20130034</t>
+  </si>
+  <si>
+    <t>OATSDE STR BR.BLN200</t>
+  </si>
+  <si>
+    <t>20087290</t>
+  </si>
+  <si>
+    <t>HILO SCHL UHT CHO200</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20134048</t>
+  </si>
+  <si>
+    <t>HILO PRTEIN CHOCO190</t>
+  </si>
+  <si>
+    <t>20053799</t>
+  </si>
+  <si>
+    <t>INDOMILK MELON 190</t>
+  </si>
+  <si>
+    <t>20136816</t>
+  </si>
+  <si>
+    <t>INDOMILK BLUEBERI190</t>
+  </si>
+  <si>
+    <t>20107748</t>
+  </si>
+  <si>
+    <t>MILKU SUSU CKLT 200</t>
+  </si>
+  <si>
+    <t>20133427</t>
+  </si>
+  <si>
+    <t>YOBICK YOG ORIGNL180</t>
+  </si>
+  <si>
+    <t>20133429</t>
+  </si>
+  <si>
+    <t>YOBICK YOG SAKURA180</t>
+  </si>
+  <si>
+    <t>10004669</t>
+  </si>
+  <si>
+    <t>ULTRA UHT CHOCO 250M</t>
+  </si>
+  <si>
+    <t>10004668</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRAW 250M</t>
+  </si>
+  <si>
+    <t>10004676</t>
+  </si>
+  <si>
+    <t>ULTRA PLAIN SLIM250M</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
+  </si>
+  <si>
+    <t>10007380</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM COKLAT200</t>
+  </si>
+  <si>
+    <t>10004401</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT VAN 180</t>
+  </si>
+  <si>
+    <t>20127735</t>
+  </si>
+  <si>
+    <t>INDMLK DLGNA COFF180</t>
+  </si>
+  <si>
+    <t>20080706</t>
+  </si>
+  <si>
+    <t>L-MEN WP 2GO CHO 200</t>
+  </si>
+  <si>
+    <t>20124409</t>
+  </si>
+  <si>
+    <t>INDOMLK STRL HNY 189</t>
+  </si>
+  <si>
+    <t>20128794</t>
+  </si>
+  <si>
+    <t>NS/GOODNES KURMA 189</t>
+  </si>
+  <si>
+    <t>20137777</t>
+  </si>
+  <si>
+    <t>NS/GOODNES HBTSD 189</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>20133540</t>
+  </si>
+  <si>
+    <t>ULTRA SSU UHT PLN750</t>
+  </si>
+  <si>
+    <t>20133541</t>
+  </si>
+  <si>
+    <t>ULTRA SSU UHT CHO750</t>
+  </si>
+  <si>
+    <t>20135532</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRW 750</t>
+  </si>
+  <si>
+    <t>20137160</t>
+  </si>
+  <si>
+    <t>ULTRA UHT MOKA 750</t>
+  </si>
+  <si>
+    <t>20077501</t>
+  </si>
+  <si>
+    <t>FF UHT COCONUT 946</t>
+  </si>
+  <si>
+    <t>20014069</t>
+  </si>
+  <si>
+    <t>FF UHT FULL CRM 946</t>
+  </si>
+  <si>
+    <t>20014071</t>
+  </si>
+  <si>
+    <t>FF UHT CHOCO 946ML</t>
+  </si>
+  <si>
+    <t>20014070</t>
+  </si>
+  <si>
+    <t>F/F LOW FAT TPK 946</t>
+  </si>
+  <si>
+    <t>20033547</t>
+  </si>
+  <si>
+    <t>GRNFIELD LOW FAT 950</t>
+  </si>
+  <si>
+    <t>20122061</t>
+  </si>
+  <si>
+    <t>OATSDE O/M B/BLND 1L</t>
+  </si>
+  <si>
+    <t>10036647</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU UHT CHO1L</t>
+  </si>
+  <si>
+    <t>10000405</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU UHT PLN1L</t>
+  </si>
+  <si>
+    <t>20017225</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT CKT 1L</t>
+  </si>
+  <si>
+    <t>10036646</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT 1000ML</t>
+  </si>
+  <si>
+    <t>10004884</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CHO 950</t>
+  </si>
+  <si>
+    <t>10005909</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT PLN 950</t>
+  </si>
+  <si>
+    <t>20033546</t>
+  </si>
+  <si>
+    <t>GRNFIELD CHOCO 950</t>
+  </si>
+  <si>
+    <t>10013027</t>
+  </si>
+  <si>
+    <t>GRNFIELD FULL CRM950</t>
+  </si>
+  <si>
+    <t>20052311</t>
+  </si>
+  <si>
+    <t>DIAMOND FULL CRM 1L</t>
+  </si>
+  <si>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
+  </si>
+  <si>
+    <t>20025359</t>
+  </si>
+  <si>
+    <t>P/SWEAT ISOTONIK2000</t>
+  </si>
+  <si>
+    <t>20136466</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE 1L</t>
+  </si>
+  <si>
+    <t>20019631</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK 1L</t>
+  </si>
+  <si>
+    <t>20076052</t>
+  </si>
+  <si>
+    <t>PUCUK TEH MLTI 1.3L</t>
+  </si>
+  <si>
+    <t>20096705</t>
+  </si>
+  <si>
+    <t>AQUA LIFE BTL 1.1L</t>
+  </si>
+  <si>
+    <t>20139700</t>
+  </si>
+  <si>
+    <t>PRISTINE 8.6  1.5L</t>
+  </si>
+  <si>
+    <t>20108983</t>
+  </si>
+  <si>
+    <t>V-SOY MULTI-GRAIN 1L</t>
+  </si>
+  <si>
+    <t>20039732</t>
+  </si>
+  <si>
+    <t>STRWAY SOYA BEAN 310</t>
+  </si>
+  <si>
+    <t>20139297</t>
+  </si>
+  <si>
+    <t>POP ICE CHOCO 5'S</t>
+  </si>
+  <si>
+    <t>20139299</t>
+  </si>
+  <si>
+    <t>POP ICE MANGO 5'S</t>
+  </si>
+  <si>
+    <t>10003389</t>
+  </si>
+  <si>
+    <t>KIRANTI SEHAT BLN150</t>
+  </si>
+  <si>
+    <t>20029054</t>
+  </si>
+  <si>
+    <t>KIRANTI JUICE 150ML</t>
+  </si>
+  <si>
+    <t>20137228</t>
+  </si>
+  <si>
+    <t>KIRANTI LYCHEE 150ML</t>
+  </si>
+  <si>
+    <t>20137229</t>
+  </si>
+  <si>
+    <t>KIRANTI BERRY 150ML</t>
+  </si>
+  <si>
+    <t>20125638</t>
+  </si>
+  <si>
+    <t>NTRSARI JRK PRS 10'S</t>
+  </si>
+  <si>
+    <t>20113377</t>
+  </si>
+  <si>
+    <t>FLRDINA COCO BIT 350</t>
+  </si>
+  <si>
+    <t>20043877</t>
+  </si>
+  <si>
+    <t>FLORIDINA ORANGE 350</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20001119</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK 4+2S</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE ICE BLACK 220</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 200</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 200</t>
+  </si>
+  <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20130354</t>
+  </si>
+  <si>
+    <t>LARISST JSMN TEA 350</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20060210</t>
+  </si>
+  <si>
+    <t>IDM TEH HJAU MLT 330</t>
+  </si>
+  <si>
+    <t>20077509</t>
+  </si>
+  <si>
+    <t>IDM LEMON TEA 330ML</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
+    <t>20015838</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 350ML</t>
+  </si>
+  <si>
+    <t>20009722</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 500ML</t>
+  </si>
+  <si>
+    <t>20019674</t>
+  </si>
+  <si>
+    <t>YOU C1000 ORG WTR500</t>
+  </si>
+  <si>
+    <t>20019673</t>
+  </si>
+  <si>
+    <t>YOU C1000 LMN WTR500</t>
+  </si>
+  <si>
+    <t>20053540</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK BTL 350</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>20018435</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 250ML</t>
+  </si>
+  <si>
+    <t>20115548</t>
+  </si>
+  <si>
+    <t>IDM COCONUT WTR 250</t>
+  </si>
+  <si>
+    <t>20128561</t>
+  </si>
+  <si>
+    <t>IDM CCNT WTR ORGE250</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
+  </si>
+  <si>
+    <t>20002504</t>
+  </si>
+  <si>
+    <t>ADEM SARI BOX 5'S</t>
+  </si>
+  <si>
+    <t>20141508</t>
+  </si>
+  <si>
+    <t>KRTINGDAENG BDD3X150</t>
+  </si>
+  <si>
     <t>14</t>
   </si>
   <si>
-    <t>20057229</t>
-  </si>
-  <si>
-    <t>VIDORAN SUSU COK 110</t>
+    <t>20121348</t>
+  </si>
+  <si>
+    <t>LASEGAR TWST J-L 320</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>20071642</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK SPRK 320</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
+  </si>
+  <si>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>10037437</t>
+  </si>
+  <si>
+    <t>C/B PENY.STRAW 320</t>
+  </si>
+  <si>
+    <t>20037150</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.LECI 320</t>
+  </si>
+  <si>
+    <t>20069199</t>
+  </si>
+  <si>
+    <t>KAKI3 LMN.LM KLG 320</t>
+  </si>
+  <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
+    <t>20055226</t>
+  </si>
+  <si>
+    <t>NTRIVE/B  STRWBRY100</t>
+  </si>
+  <si>
+    <t>20082247</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL ORG 100</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20115157</t>
+  </si>
+  <si>
+    <t>BUAVITA ORANGE 1L</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>20113180</t>
-  </si>
-  <si>
-    <t>MILO COKLAT 4X110ML</t>
-  </si>
-  <si>
-    <t>20083931</t>
-  </si>
-  <si>
-    <t>MILO ACT-GO 4X180ML</t>
-  </si>
-  <si>
-    <t>20130034</t>
-  </si>
-  <si>
-    <t>OATSDE STR BR.BLN200</t>
-  </si>
-  <si>
-    <t>20133859</t>
-  </si>
-  <si>
-    <t>OATSIDE CHCOMALT200</t>
-  </si>
-  <si>
-    <t>20134556</t>
-  </si>
-  <si>
-    <t>OATSIDE MOCHA 200</t>
-  </si>
-  <si>
-    <t>20087290</t>
-  </si>
-  <si>
-    <t>HILO SCHL UHT CHO200</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20053799</t>
-  </si>
-  <si>
-    <t>INDOMILK MELON 190</t>
-  </si>
-  <si>
-    <t>20136816</t>
-  </si>
-  <si>
-    <t>INDOMILK BLUEBERI190</t>
-  </si>
-  <si>
-    <t>20107748</t>
-  </si>
-  <si>
-    <t>MILKU SUSU CKLT 200</t>
-  </si>
-  <si>
-    <t>10004669</t>
-  </si>
-  <si>
-    <t>ULTRA UHT CHOCO 250M</t>
-  </si>
-  <si>
-    <t>10004668</t>
-  </si>
-  <si>
-    <t>ULTRA UHT STRAW 250M</t>
-  </si>
-  <si>
-    <t>10004676</t>
-  </si>
-  <si>
-    <t>ULTRA PLAIN SLIM250M</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
-    <t>10007380</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM COKLAT200</t>
-  </si>
-  <si>
-    <t>10004401</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT VAN 180</t>
-  </si>
-  <si>
-    <t>20127735</t>
-  </si>
-  <si>
-    <t>INDMLK DLGNA COFF180</t>
-  </si>
-  <si>
-    <t>20080706</t>
-  </si>
-  <si>
-    <t>L-MEN WP 2GO CHO 200</t>
-  </si>
-  <si>
-    <t>20124409</t>
-  </si>
-  <si>
-    <t>INDOMLK STRL HNY 189</t>
-  </si>
-  <si>
-    <t>20128794</t>
-  </si>
-  <si>
-    <t>NS/GOODNES KURMA 189</t>
-  </si>
-  <si>
-    <t>20137777</t>
-  </si>
-  <si>
-    <t>NS/GOODNES HBTSD 189</t>
-  </si>
-  <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CLGEN 189</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>20133540</t>
-  </si>
-  <si>
-    <t>ULTRA SSU UHT PLN750</t>
-  </si>
-  <si>
-    <t>20133541</t>
-  </si>
-  <si>
-    <t>ULTRA SSU UHT CHO750</t>
-  </si>
-  <si>
-    <t>20135532</t>
-  </si>
-  <si>
-    <t>ULTRA UHT STRW 750</t>
-  </si>
-  <si>
-    <t>20137160</t>
-  </si>
-  <si>
-    <t>ULTRA UHT MOKA 750</t>
-  </si>
-  <si>
-    <t>20077501</t>
-  </si>
-  <si>
-    <t>FF UHT COCONUT 946</t>
-  </si>
-  <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
-  </si>
-  <si>
-    <t>20014071</t>
-  </si>
-  <si>
-    <t>FF UHT CHOCO 946ML</t>
-  </si>
-  <si>
-    <t>20014070</t>
-  </si>
-  <si>
-    <t>F/F LOW FAT TPK 946</t>
-  </si>
-  <si>
-    <t>20033547</t>
-  </si>
-  <si>
-    <t>GRNFIELD LOW FAT 950</t>
-  </si>
-  <si>
-    <t>20122061</t>
-  </si>
-  <si>
-    <t>OATSDE O/M B/BLND 1L</t>
-  </si>
-  <si>
-    <t>10036647</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU UHT CHO1L</t>
-  </si>
-  <si>
-    <t>10000405</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU UHT PLN1L</t>
-  </si>
-  <si>
-    <t>20017225</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT CKT 1L</t>
-  </si>
-  <si>
-    <t>10036646</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT 1000ML</t>
-  </si>
-  <si>
-    <t>10004884</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CHO 950</t>
-  </si>
-  <si>
-    <t>10005909</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT PLN 950</t>
-  </si>
-  <si>
-    <t>20033546</t>
-  </si>
-  <si>
-    <t>GRNFIELD CHOCO 950</t>
-  </si>
-  <si>
-    <t>10013027</t>
-  </si>
-  <si>
-    <t>GRNFIELD FULL CRM950</t>
-  </si>
-  <si>
-    <t>20052311</t>
-  </si>
-  <si>
-    <t>DIAMOND FULL CRM 1L</t>
-  </si>
-  <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 330</t>
-  </si>
-  <si>
-    <t>20025359</t>
-  </si>
-  <si>
-    <t>P/SWEAT ISOTONIK2000</t>
-  </si>
-  <si>
-    <t>20136466</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE 1L</t>
-  </si>
-  <si>
-    <t>20019631</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK 1L</t>
-  </si>
-  <si>
-    <t>20076052</t>
-  </si>
-  <si>
-    <t>PUCUK TEH MLTI 1.3L</t>
-  </si>
-  <si>
-    <t>20096705</t>
-  </si>
-  <si>
-    <t>AQUA LIFE BTL 1.1L</t>
-  </si>
-  <si>
-    <t>20139700</t>
-  </si>
-  <si>
-    <t>PRISTINE 8.6  1.5L</t>
-  </si>
-  <si>
-    <t>20108983</t>
-  </si>
-  <si>
-    <t>V-SOY MULTI-GRAIN 1L</t>
-  </si>
-  <si>
-    <t>20039732</t>
-  </si>
-  <si>
-    <t>STRWAY SOYA BEAN 310</t>
-  </si>
-  <si>
-    <t>20139297</t>
-  </si>
-  <si>
-    <t>POP ICE CHOCO 5'S</t>
-  </si>
-  <si>
-    <t>20139299</t>
-  </si>
-  <si>
-    <t>POP ICE MANGO 5'S</t>
-  </si>
-  <si>
-    <t>20002504</t>
-  </si>
-  <si>
-    <t>ADEM SARI BOX 5'S</t>
-  </si>
-  <si>
-    <t>10003389</t>
-  </si>
-  <si>
-    <t>KIRANTI SEHAT BLN150</t>
-  </si>
-  <si>
-    <t>20029054</t>
-  </si>
-  <si>
-    <t>KIRANTI JUICE 150ML</t>
-  </si>
-  <si>
-    <t>20137228</t>
-  </si>
-  <si>
-    <t>KIRANTI LYCHEE 150ML</t>
-  </si>
-  <si>
-    <t>20137229</t>
-  </si>
-  <si>
-    <t>KIRANTI BERRY 150ML</t>
-  </si>
-  <si>
-    <t>20125638</t>
-  </si>
-  <si>
-    <t>NTRSARI JRK PRS 10'S</t>
-  </si>
-  <si>
-    <t>20113377</t>
-  </si>
-  <si>
-    <t>FLRDINA COCO BIT 350</t>
-  </si>
-  <si>
-    <t>20043877</t>
-  </si>
-  <si>
-    <t>FLORIDINA ORANGE 350</t>
-  </si>
-  <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NESCAFE CPUCCINO 220</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NESCAFE LATTE 220ML</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE ICE BLACK 220</t>
-  </si>
-  <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20102789</t>
-  </si>
-  <si>
-    <t>ABC CHOCMLT COFF 200</t>
-  </si>
-  <si>
-    <t>20102790</t>
-  </si>
-  <si>
-    <t>ABC MILK COFFEE 200</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20130354</t>
-  </si>
-  <si>
-    <t>LARISST JSMN TEA 350</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20060210</t>
-  </si>
-  <si>
-    <t>IDM TEH HJAU MLT 330</t>
-  </si>
-  <si>
-    <t>20077509</t>
-  </si>
-  <si>
-    <t>IDM LEMON TEA 330ML</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
-  </si>
-  <si>
-    <t>20015838</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 350ML</t>
-  </si>
-  <si>
-    <t>20009722</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 500ML</t>
-  </si>
-  <si>
-    <t>20019674</t>
-  </si>
-  <si>
-    <t>YOU C1000 ORG WTR500</t>
-  </si>
-  <si>
-    <t>20019673</t>
-  </si>
-  <si>
-    <t>YOU C1000 LMN WTR500</t>
+    <t>20067201</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGO TPK 1L</t>
+  </si>
+  <si>
+    <t>20067200</t>
+  </si>
+  <si>
+    <t>BUAVITA GUAVA TPK 1L</t>
+  </si>
+  <si>
+    <t>20116490</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 1L</t>
   </si>
   <si>
     <t>20127835</t>
   </si>
   <si>
     <t>ALANG SARI JN 300ML</t>
-  </si>
-  <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
-  </si>
-  <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>20018435</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 250ML</t>
-  </si>
-  <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20128561</t>
-  </si>
-  <si>
-    <t>IDM CCNT WTR ORGE250</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
-  </si>
-  <si>
-    <t>20121348</t>
-  </si>
-  <si>
-    <t>LASEGAR TWST J-L 320</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>10037437</t>
-  </si>
-  <si>
-    <t>C/B PENY.STRAW 320</t>
-  </si>
-  <si>
-    <t>20037150</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.LECI 320</t>
-  </si>
-  <si>
-    <t>20069199</t>
-  </si>
-  <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
-  </si>
-  <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
-  </si>
-  <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
-  </si>
-  <si>
-    <t>20055226</t>
-  </si>
-  <si>
-    <t>NTRIVE/B  STRWBRY100</t>
-  </si>
-  <si>
-    <t>20082247</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL ORG 100</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20115157</t>
-  </si>
-  <si>
-    <t>BUAVITA ORANGE 1L</t>
-  </si>
-  <si>
-    <t>20067201</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGO TPK 1L</t>
-  </si>
-  <si>
-    <t>20067200</t>
-  </si>
-  <si>
-    <t>BUAVITA GUAVA TPK 1L</t>
-  </si>
-  <si>
-    <t>20116490</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 1L</t>
   </si>
   <si>
     <t>20130801</t>
@@ -1600,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2447,7 +2453,7 @@
         <v>73</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2461,10 +2467,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>34</v>
@@ -2472,30 +2478,30 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2504,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>34</v>
@@ -2512,10 +2518,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2524,18 +2530,18 @@
         <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2544,7 +2550,7 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>34</v>
@@ -2552,10 +2558,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2564,7 +2570,7 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>34</v>
@@ -2572,10 +2578,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2584,7 +2590,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>34</v>
@@ -2592,10 +2598,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2604,18 +2610,18 @@
         <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2624,7 +2630,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>34</v>
@@ -2632,10 +2638,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2644,7 +2650,7 @@
         <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>34</v>
@@ -2652,19 +2658,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>34</v>
@@ -2672,10 +2678,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2684,7 +2690,7 @@
         <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>34</v>
@@ -2692,10 +2698,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2704,7 +2710,7 @@
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>34</v>
@@ -2712,10 +2718,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2724,7 +2730,7 @@
         <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>34</v>
@@ -2732,10 +2738,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2744,7 +2750,7 @@
         <v>21</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>34</v>
@@ -2752,10 +2758,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2764,7 +2770,7 @@
         <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>34</v>
@@ -2772,10 +2778,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2784,7 +2790,7 @@
         <v>21</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>34</v>
@@ -2792,10 +2798,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2804,7 +2810,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>34</v>
@@ -2812,10 +2818,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2824,7 +2830,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>34</v>
@@ -2832,10 +2838,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2844,7 +2850,7 @@
         <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>34</v>
@@ -2852,10 +2858,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2864,7 +2870,7 @@
         <v>21</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>34</v>
@@ -2872,10 +2878,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2884,7 +2890,7 @@
         <v>21</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>34</v>
@@ -2892,10 +2898,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2904,7 +2910,7 @@
         <v>21</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>34</v>
@@ -2912,19 +2918,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>34</v>
@@ -2932,10 +2938,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2944,7 +2950,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>34</v>
@@ -2952,10 +2958,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2964,7 +2970,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>34</v>
@@ -2972,10 +2978,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2984,7 +2990,7 @@
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>34</v>
@@ -2992,10 +2998,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -3004,7 +3010,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>34</v>
@@ -3012,10 +3018,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -3024,7 +3030,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>34</v>
@@ -3032,10 +3038,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -3044,7 +3050,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>34</v>
@@ -3052,10 +3058,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -3064,7 +3070,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>34</v>
@@ -3072,10 +3078,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -3084,7 +3090,7 @@
         <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>34</v>
@@ -3092,10 +3098,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -3104,7 +3110,7 @@
         <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>34</v>
@@ -3112,19 +3118,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>34</v>
@@ -3132,10 +3138,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3144,7 +3150,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>34</v>
@@ -3152,10 +3158,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -3164,7 +3170,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>34</v>
@@ -3172,10 +3178,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3184,7 +3190,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>34</v>
@@ -3192,10 +3198,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3204,7 +3210,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>34</v>
@@ -3212,10 +3218,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3224,7 +3230,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>34</v>
@@ -3232,10 +3238,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -3244,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>34</v>
@@ -3252,10 +3258,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -3264,7 +3270,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>34</v>
@@ -3272,10 +3278,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3284,7 +3290,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>34</v>
@@ -3292,19 +3298,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>34</v>
@@ -3312,10 +3318,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3324,18 +3330,18 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3344,18 +3350,18 @@
         <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3364,7 +3370,7 @@
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>34</v>
@@ -3372,10 +3378,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3384,7 +3390,7 @@
         <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>34</v>
@@ -3392,10 +3398,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3404,18 +3410,18 @@
         <v>30</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3424,38 +3430,38 @@
         <v>30</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3464,18 +3470,18 @@
         <v>33</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3484,18 +3490,18 @@
         <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3504,7 +3510,7 @@
         <v>33</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>34</v>
@@ -3512,10 +3518,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3524,7 +3530,7 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>34</v>
@@ -3532,10 +3538,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3544,7 +3550,7 @@
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>34</v>
@@ -3552,10 +3558,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3564,7 +3570,7 @@
         <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>34</v>
@@ -3572,10 +3578,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3584,7 +3590,7 @@
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>34</v>
@@ -3592,10 +3598,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3604,7 +3610,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3612,10 +3618,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3624,7 +3630,7 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3632,10 +3638,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3644,7 +3650,7 @@
         <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3652,19 +3658,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3672,19 +3678,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3692,10 +3698,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3704,7 +3710,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3712,10 +3718,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3724,7 +3730,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3732,10 +3738,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3744,7 +3750,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3752,10 +3758,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3764,7 +3770,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3772,10 +3778,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3784,18 +3790,18 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3804,18 +3810,18 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3824,18 +3830,18 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3844,18 +3850,18 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3864,7 +3870,7 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>34</v>
@@ -3872,10 +3878,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3884,18 +3890,18 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3904,7 +3910,7 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3912,30 +3918,30 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3944,7 +3950,7 @@
         <v>70</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>34</v>
@@ -3952,10 +3958,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3964,7 +3970,7 @@
         <v>70</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>34</v>
@@ -3972,10 +3978,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3984,7 +3990,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -3992,10 +3998,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4004,7 +4010,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4012,10 +4018,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4024,7 +4030,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4032,10 +4038,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4044,7 +4050,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4052,10 +4058,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4064,7 +4070,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4072,10 +4078,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4084,18 +4090,18 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>34</v>
+        <v>266</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4104,18 +4110,18 @@
         <v>70</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4124,18 +4130,18 @@
         <v>70</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4144,38 +4150,38 @@
         <v>70</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>270</v>
+        <v>109</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4184,18 +4190,18 @@
         <v>73</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4204,18 +4210,18 @@
         <v>73</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4224,7 +4230,7 @@
         <v>73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>34</v>
@@ -4232,10 +4238,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4244,7 +4250,7 @@
         <v>73</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>34</v>
@@ -4252,10 +4258,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4264,18 +4270,18 @@
         <v>73</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4284,18 +4290,18 @@
         <v>73</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4304,18 +4310,18 @@
         <v>73</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4324,18 +4330,18 @@
         <v>73</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4344,18 +4350,18 @@
         <v>73</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>270</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4364,18 +4370,18 @@
         <v>73</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>270</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4384,7 +4390,7 @@
         <v>73</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4392,10 +4398,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4404,7 +4410,7 @@
         <v>73</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>34</v>
@@ -4412,10 +4418,10 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
@@ -4424,7 +4430,7 @@
         <v>73</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>73</v>
+        <v>301</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>34</v>
@@ -4432,36 +4438,36 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>8</v>
@@ -4472,16 +4478,16 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>11</v>
@@ -4492,16 +4498,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>15</v>
@@ -4512,16 +4518,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>18</v>
@@ -4532,16 +4538,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>21</v>
@@ -4552,16 +4558,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>24</v>
@@ -4572,16 +4578,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>27</v>
@@ -4592,16 +4598,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>30</v>
@@ -4612,16 +4618,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>33</v>
@@ -4632,16 +4638,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>37</v>
@@ -4652,16 +4658,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>70</v>
@@ -4672,16 +4678,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>73</v>
@@ -4692,36 +4698,36 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>4</v>
@@ -4741,7 +4747,7 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>8</v>
@@ -4761,7 +4767,7 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>11</v>
@@ -4781,7 +4787,7 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>15</v>
@@ -4801,7 +4807,7 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>18</v>
@@ -4821,7 +4827,7 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>21</v>
@@ -4841,13 +4847,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4861,7 +4867,7 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>27</v>
@@ -4881,33 +4887,33 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>119</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4921,10 +4927,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4941,10 +4947,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4961,13 +4967,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>270</v>
+        <v>34</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4981,33 +4987,33 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>12</v>
+        <v>266</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5021,93 +5027,93 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>366</v>
+        <v>34</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>366</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>34</v>
+        <v>368</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5121,10 +5127,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>34</v>
@@ -5141,10 +5147,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>34</v>
@@ -5161,13 +5167,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5181,73 +5187,73 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>389</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -5261,13 +5267,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5281,13 +5287,33 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E184" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F184" s="1" t="s">
-        <v>119</v>
+      <c r="F185" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
